--- a/data/My_Pitcher_Listing.xlsx
+++ b/data/My_Pitcher_Listing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29923"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn\Python\sports_dash_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B02236D-493E-48B1-872E-10AA8F00A7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB3F8F2D-2564-4CF4-A43B-5D176DD4D064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48223,7 +48223,7 @@
         <v>21</v>
       </c>
       <c r="C769" t="s">
-        <v>46</v>
+        <v>157</v>
       </c>
       <c r="D769" t="s">
         <v>47</v>

--- a/data/My_Pitcher_Listing.xlsx
+++ b/data/My_Pitcher_Listing.xlsx
@@ -43533,10 +43533,10 @@
         <v>1565</v>
       </c>
       <c r="C675" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="D675" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="E675" t="s">
         <v>1626</v>
@@ -43562,6 +43562,9 @@
       <c r="M675" t="s">
         <v>693</v>
       </c>
+      <c r="N675">
+        <v>1</v>
+      </c>
       <c r="P675" t="s">
         <v>693</v>
       </c>
@@ -43572,7 +43575,7 @@
         <v>693</v>
       </c>
       <c r="T675" t="s">
-        <v>3025</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="676" spans="1:20">
